--- a/UTCUTS/A1_Outputs/reference_works/A-O_AR_Projections_REF.xlsx
+++ b/UTCUTS/A1_Outputs/reference_works/A-O_AR_Projections_REF.xlsx
@@ -10475,7 +10475,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89EA89C9-A611-4DBE-AF1A-DB27CED9724A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65251340-A73D-4951-A425-808E4B57B6D6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
